--- a/jogos_2025-02-04.xlsx
+++ b/jogos_2025-02-04.xlsx
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.41</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>6.7</v>
+        <v>3.24</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>10.05</v>
       </c>
       <c r="O5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>11</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['7', '39', '48', '51']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>5.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['35', '50', '61']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45692.58333333334</v>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>5.07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.84</v>
+        <v>4.33</v>
       </c>
       <c r="N6" t="n">
-        <v>8.640000000000001</v>
+        <v>1.47</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['31', '71']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45692.58333333334</v>
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>3.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.76</v>
+        <v>2.13</v>
       </c>
       <c r="N7" t="n">
-        <v>8.210000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1372,14 +1372,14 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>['67', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45692.58333333334</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.07</v>
+        <v>2.37</v>
       </c>
       <c r="M8" t="n">
-        <v>4.33</v>
+        <v>1.76</v>
       </c>
       <c r="N8" t="n">
-        <v>1.47</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="O8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.63</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,19 +1494,19 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG8" t="n">
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45692.58333333334</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.25</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['31', '71']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['52', '90+7']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45692.58333333334</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>2.13</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,14 +1752,14 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['67', '90+5']</t>
+          <t>['52', '90+7']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45692.58333333334</v>
@@ -1804,54 +1804,54 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.83</v>
+        <v>5.41</v>
       </c>
       <c r="M11" t="n">
-        <v>1.34</v>
+        <v>6.7</v>
       </c>
       <c r="N11" t="n">
-        <v>6.3</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2.75</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1881,19 +1881,19 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['35', '50', '61']</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45692.58333333334</v>
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,34 +1959,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>4.83</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24</v>
+        <v>1.34</v>
       </c>
       <c r="N12" t="n">
-        <v>10.05</v>
+        <v>6.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q12" t="n">
-        <v>11</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2001,41 +2001,41 @@
         <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['7', '39', '48', '51']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45692.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FC Schaffhausen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.67</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['90+8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.96</v>
+        <v>1.45</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45692.64583333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Schaffhausen</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.36</v>
+        <v>3.57</v>
       </c>
       <c r="N18" t="n">
-        <v>2.27</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y18" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.2</v>
       </c>
-      <c r="X18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>['90+8']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
       <c r="AG18" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45692.64583333334</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P19" t="n">
         <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
         <v>1.35</v>
@@ -2898,7 +2898,7 @@
         <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Y19" t="n">
         <v>1.79</v>
@@ -2913,32 +2913,32 @@
         <v>1.38</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['64', '79']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['29', '85']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['13', '85', '89']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['45', '53', '90+8']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45692.6875</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="M20" t="n">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="N20" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
         <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
         <v>1.35</v>
@@ -3027,7 +3027,7 @@
         <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
         <v>1.79</v>
@@ -3042,32 +3042,32 @@
         <v>1.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['64', '79']</t>
+          <t>['13', '85', '89']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['29', '85']</t>
+          <t>['45', '53', '90+8']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45692.6875</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>3.37</v>
+        <v>2.79</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X21" t="n">
         <v>3.75</v>
       </c>
-      <c r="R21" t="n">
+      <c r="Y21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['8', '82']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['62', '77', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['13', '38', '51']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
         <v>1.62</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45692.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O22" t="n">
         <v>2.05</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.75</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45692.69791666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,80 +3378,80 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="M23" t="n">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="N23" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['8', '82']</t>
+          <t>['5', '76']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AJ23" t="n">
         <v>2.1</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -3507,28 +3507,28 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>9.800000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
         <v>3.25</v>
@@ -3537,53 +3537,53 @@
         <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66', '83']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.75</v>
+        <v>1.12</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.36</v>
+        <v>3.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.7</v>
+        <v>1.44</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45692.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['5', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45692.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>3.37</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['62', '77', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['13', '38', '51']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['66', '83']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45692.69791666666</v>
